--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484739_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484739_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T. BOUNDI</t>
+          <t>M. VARELA BARCIA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.4161</v>
+        <v>10.1263</v>
       </c>
       <c r="E2" t="n">
-        <v>8.991400000000001</v>
+        <v>6.6292</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4247</v>
+        <v>3.497</v>
       </c>
       <c r="G2" t="n">
-        <v>5.4633</v>
+        <v>7.2742</v>
       </c>
       <c r="H2" t="n">
-        <v>3.9239</v>
+        <v>-2.8784</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5394</v>
+        <v>10.1526</v>
       </c>
       <c r="J2" t="n">
-        <v>5.9521</v>
+        <v>7.5189</v>
       </c>
       <c r="K2" t="n">
-        <v>4.9976</v>
+        <v>-2.0489</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9545</v>
+        <v>9.5677</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4888</v>
+        <v>-0.2447</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.0737</v>
+        <v>-0.8295</v>
       </c>
       <c r="O2" t="n">
         <v>0.5849</v>
       </c>
       <c r="P2" t="n">
-        <v>3.0192</v>
+        <v>2.8305</v>
       </c>
       <c r="Q2" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R2" t="n">
-        <v>3.9627</v>
+        <v>3.774</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5752</v>
+        <v>0.0216</v>
       </c>
       <c r="T2" t="n">
-        <v>4.0207</v>
+        <v>0.0539</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4455</v>
+        <v>-0.0323</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.038</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. VARELA BARCIA</t>
+          <t>T. BOUNDI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.926</v>
+        <v>8.931900000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6936</v>
+        <v>6.322</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2325</v>
+        <v>2.6099</v>
       </c>
       <c r="G3" t="n">
-        <v>7.2742</v>
+        <v>5.4633</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.8784</v>
+        <v>3.9239</v>
       </c>
       <c r="I3" t="n">
-        <v>10.1526</v>
+        <v>1.5394</v>
       </c>
       <c r="J3" t="n">
-        <v>7.5189</v>
+        <v>5.9521</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.0489</v>
+        <v>4.9976</v>
       </c>
       <c r="L3" t="n">
-        <v>9.5677</v>
+        <v>0.9545</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2447</v>
+        <v>-0.4888</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8295</v>
+        <v>-1.0737</v>
       </c>
       <c r="O3" t="n">
         <v>0.5849</v>
       </c>
       <c r="P3" t="n">
-        <v>2.8305</v>
+        <v>3.0192</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R3" t="n">
-        <v>3.774</v>
+        <v>3.9627</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1786</v>
+        <v>1.091</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8818</v>
+        <v>1.3514</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2968</v>
+        <v>-0.2604</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>-0.038</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. GONZALEZ DIAZ</t>
+          <t>P. GOMEZ GARCIA-GUTIERREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.1336</v>
+        <v>5.6358</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3561</v>
+        <v>2.019</v>
       </c>
       <c r="F4" t="n">
-        <v>3.7775</v>
+        <v>3.6168</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6933</v>
+        <v>1.8234</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1456</v>
+        <v>-0.9063</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5477</v>
+        <v>2.7296</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1888</v>
+        <v>1.9651</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8139</v>
+        <v>-0.1581</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.0027</v>
+        <v>2.1232</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5044999999999999</v>
+        <v>-0.1417</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9595</v>
+        <v>-0.7482</v>
       </c>
       <c r="O4" t="n">
-        <v>0.455</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>3.5853</v>
+        <v>3.774</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.5853</v>
+        <v>3.774</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9964</v>
+        <v>0.3402</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2997</v>
+        <v>0.0539</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6967</v>
+        <v>0.2863</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2452</v>
+        <v>-0.3018</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. GOMEZ GARCIA-GUTIERREZ</t>
+          <t>C. GONZALEZ DIAZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.753</v>
+        <v>4.4504</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0833</v>
+        <v>1.1226</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6697</v>
+        <v>3.3277</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8234</v>
+        <v>-0.6933</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9063</v>
+        <v>-0.1456</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7296</v>
+        <v>-0.5477</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9651</v>
+        <v>-0.1888</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1581</v>
+        <v>0.8139</v>
       </c>
       <c r="L5" t="n">
-        <v>2.1232</v>
+        <v>-1.0027</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1417</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7482</v>
+        <v>-0.9595</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.455</v>
       </c>
       <c r="P5" t="n">
-        <v>3.774</v>
+        <v>3.5853</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.774</v>
+        <v>3.5853</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5426</v>
+        <v>0.3132</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8818</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3392</v>
+        <v>0.2469</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3018</v>
+        <v>1.2452</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.5948</v>
+        <v>3.8832</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3044</v>
+        <v>3.4607</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2903</v>
+        <v>0.4226</v>
       </c>
       <c r="G6" t="n">
         <v>2.7589</v>
@@ -922,13 +922,13 @@
         <v>3.2079</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1375</v>
+        <v>0.426</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0646</v>
+        <v>0.2208</v>
       </c>
       <c r="U6" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.2052</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6226</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2516</v>
+        <v>1.4541</v>
       </c>
       <c r="E7" t="n">
-        <v>2.3876</v>
+        <v>1.5107</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.136</v>
+        <v>-0.0566</v>
       </c>
       <c r="G7" t="n">
         <v>0.1033</v>
@@ -1000,13 +1000,13 @@
         <v>0.9435</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5066</v>
+        <v>0.7091</v>
       </c>
       <c r="T7" t="n">
-        <v>1.596</v>
+        <v>0.7191</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0893</v>
+        <v>-0.01</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3018</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.324</v>
+        <v>0.3504</v>
       </c>
       <c r="E8" t="n">
         <v>1.4329</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.109</v>
+        <v>-1.0825</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0643</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1587</v>
+        <v>-0.1323</v>
       </c>
       <c r="T8" t="n">
         <v>-0.1764</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0176</v>
+        <v>0.0441</v>
       </c>
       <c r="V8" t="n">
         <v>1.547</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4652</v>
+        <v>-0.7689</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0157</v>
+        <v>0.6277</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4495</v>
+        <v>-1.3966</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3683</v>
@@ -1234,13 +1234,13 @@
         <v>0.3774</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5308</v>
+        <v>0.1655</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5291</v>
+        <v>0.1143</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0017</v>
+        <v>0.0512</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.624</v>
+        <v>-1.107</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2182</v>
+        <v>-2.516</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5943</v>
+        <v>1.4091</v>
       </c>
       <c r="G11" t="n">
         <v>-2.025</v>
@@ -1312,13 +1312,13 @@
         <v>1.5096</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4667</v>
+        <v>0.0503</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.823</v>
+        <v>-0.1208</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3563</v>
+        <v>0.1711</v>
       </c>
       <c r="V11" t="n">
         <v>1.2452</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.8753</v>
+        <v>-4.0967</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8081</v>
+        <v>-2.0029</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0673</v>
+        <v>-2.0937</v>
       </c>
       <c r="G12" t="n">
         <v>-2.5537</v>
@@ -1390,13 +1390,13 @@
         <v>0.5661</v>
       </c>
       <c r="S12" t="n">
-        <v>0.301</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2968</v>
+        <v>0.102</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0041</v>
+        <v>-0.0223</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2452</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.2413</v>
+        <v>-4.6508</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.8851</v>
+        <v>-1.2417</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.3562</v>
+        <v>-3.4091</v>
       </c>
       <c r="G13" t="n">
         <v>-1.076</v>
@@ -1468,13 +1468,13 @@
         <v>1.1322</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.92</v>
+        <v>-0.3295</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8818</v>
+        <v>-0.2384</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0382</v>
+        <v>-0.0911</v>
       </c>
       <c r="V13" t="n">
         <v>-1.547</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.6233</v>
+        <v>-5.0509</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.7526</v>
+        <v>-2.2067</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.8707</v>
+        <v>-2.8442</v>
       </c>
       <c r="G14" t="n">
         <v>-4.6012</v>
@@ -1546,13 +1546,13 @@
         <v>0.7548</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2299</v>
+        <v>0.3426</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5291</v>
+        <v>0.0169</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2992</v>
+        <v>0.3257</v>
       </c>
       <c r="V14" t="n">
         <v>-1.547</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>18.887</v>
+        <v>19.47479999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>14.8866</v>
+        <v>15.4745</v>
       </c>
       <c r="F15" t="n">
-        <v>4.000300000000001</v>
+        <v>4.0004</v>
       </c>
       <c r="G15" t="n">
         <v>5.358300000000002</v>
@@ -1624,13 +1624,13 @@
         <v>23.5875</v>
       </c>
       <c r="S15" t="n">
-        <v>2.489400000000001</v>
+        <v>3.0774</v>
       </c>
       <c r="T15" t="n">
-        <v>1.574799999999999</v>
+        <v>2.1629</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9145000000000001</v>
+        <v>0.9144000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>-2.1696</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.1058</v>
+        <v>3.9475</v>
       </c>
       <c r="E16" t="n">
-        <v>6.5086</v>
+        <v>5.8265</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4028</v>
+        <v>-1.879</v>
       </c>
       <c r="G16" t="n">
         <v>1.6877</v>
@@ -1702,13 +1702,13 @@
         <v>1.887</v>
       </c>
       <c r="S16" t="n">
-        <v>1.211</v>
+        <v>0.0528</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7141</v>
+        <v>0.0321</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4969</v>
+        <v>0.0207</v>
       </c>
       <c r="V16" t="n">
         <v>3.7166</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8939</v>
+        <v>0.7267</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4248</v>
+        <v>1.5222</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5309</v>
+        <v>-0.7954</v>
       </c>
       <c r="G18" t="n">
         <v>2.2934</v>
@@ -1858,13 +1858,13 @@
         <v>1.1322</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3745</v>
+        <v>0.2074</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2323</v>
+        <v>-0.1348</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6068</v>
+        <v>0.3422</v>
       </c>
       <c r="V18" t="n">
         <v>1.2452</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.892</v>
+        <v>0.4229</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3924</v>
+        <v>1.0027</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5004</v>
+        <v>-0.5797</v>
       </c>
       <c r="G19" t="n">
         <v>2.1018</v>
@@ -1936,13 +1936,13 @@
         <v>0.5661</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2998</v>
+        <v>-0.1693</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4144</v>
+        <v>0.0247</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1146</v>
+        <v>-0.194</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1035</v>
+        <v>0.4185</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6888</v>
+        <v>1.0785</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7923</v>
+        <v>-0.66</v>
       </c>
       <c r="G20" t="n">
         <v>0.127</v>
@@ -2014,13 +2014,13 @@
         <v>0.7548</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7965</v>
+        <v>-0.2745</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5879</v>
+        <v>-0.1981</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2087</v>
+        <v>-0.0764</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2825</v>
+        <v>-2.3896</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0498</v>
+        <v>-0.3421</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2327</v>
+        <v>-2.0475</v>
       </c>
       <c r="G21" t="n">
         <v>-2.4137</v>
@@ -2092,13 +2092,13 @@
         <v>0.1887</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1705</v>
+        <v>-0.2776</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3556</v>
+        <v>0.0633</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5261</v>
+        <v>-0.3409</v>
       </c>
       <c r="V21" t="n">
         <v>1.2452</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.8238</v>
+        <v>-4.1527</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.3565</v>
+        <v>-3.1617</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4673</v>
+        <v>-0.9911</v>
       </c>
       <c r="G22" t="n">
         <v>-2.5662</v>
@@ -2170,13 +2170,13 @@
         <v>1.887</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0499</v>
+        <v>-0.3788</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3498</v>
+        <v>-0.155</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7000999999999999</v>
+        <v>-0.2239</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6415999999999999</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. MARTIN MARTINEZ</t>
+          <t>G. GARCIA CARCASES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.0209</v>
+        <v>-5.8225</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5097</v>
+        <v>-2.8212</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.5113</v>
+        <v>-3.0013</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.7596</v>
+        <v>1.1496</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3123</v>
+        <v>0.4719</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.0719</v>
+        <v>0.6776</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8143</v>
+        <v>2.6297</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4437</v>
+        <v>1.8227</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.258</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.9453</v>
+        <v>-1.4801</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1315</v>
+        <v>-1.3507</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.8139</v>
+        <v>-0.1294</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.3209</v>
+        <v>-3.3966</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.6983</v>
+        <v>-5.0949</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3774</v>
+        <v>1.6983</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3368</v>
+        <v>-0.7833</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0029</v>
+        <v>-0.356</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3397</v>
+        <v>-0.4273</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6036</v>
+        <v>-2.7922</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.6036</v>
+        <v>-2.7922</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>G. GARCIA CARCASES</t>
+          <t>M. MARTIN MARTINEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.4865</v>
+        <v>-6.039</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.4058</v>
+        <v>-2.6071</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.0807</v>
+        <v>-3.4319</v>
       </c>
       <c r="G24" t="n">
-        <v>1.1496</v>
+        <v>-3.7596</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4719</v>
+        <v>0.3123</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6776</v>
+        <v>-4.0719</v>
       </c>
       <c r="J24" t="n">
-        <v>2.6297</v>
+        <v>-0.8143</v>
       </c>
       <c r="K24" t="n">
-        <v>1.8227</v>
+        <v>0.4437</v>
       </c>
       <c r="L24" t="n">
-        <v>0.8070000000000001</v>
+        <v>-1.258</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.4801</v>
+        <v>-2.9453</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.3507</v>
+        <v>-0.1315</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1294</v>
+        <v>-2.8139</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.3966</v>
+        <v>-1.3209</v>
       </c>
       <c r="Q24" t="n">
-        <v>-5.0949</v>
+        <v>-1.6983</v>
       </c>
       <c r="R24" t="n">
-        <v>1.6983</v>
+        <v>0.3774</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4472</v>
+        <v>-0.3549</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9406</v>
+        <v>-0.0945</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5066000000000001</v>
+        <v>-0.2604</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.7922</v>
+        <v>-0.6036</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.7922</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.6122</v>
+        <v>-7.5496</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.2438</v>
+        <v>-6.049</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.3684</v>
+        <v>-1.5007</v>
       </c>
       <c r="G25" t="n">
         <v>-5.5289</v>
@@ -2404,13 +2404,13 @@
         <v>1.887</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5737</v>
+        <v>-0.5111</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.291</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2827</v>
+        <v>-0.4149</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-18.8868</v>
+        <v>-18.8869</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.000100000000001</v>
+        <v>-4.000300000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-14.8868</v>
+        <v>-14.8866</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.357999999999999</v>
+        <v>-5.358</v>
       </c>
       <c r="H26" t="n">
-        <v>3.083499999999999</v>
+        <v>3.0835</v>
       </c>
       <c r="I26" t="n">
         <v>-8.441700000000001</v>
@@ -2467,7 +2467,7 @@
         <v>-19.6909</v>
       </c>
       <c r="N26" t="n">
-        <v>-9.195399999999999</v>
+        <v>-9.195400000000001</v>
       </c>
       <c r="O26" t="n">
         <v>-10.4956</v>
@@ -2485,10 +2485,10 @@
         <v>-2.4893</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.9146000000000001</v>
+        <v>-0.9145</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.5748</v>
+        <v>-1.5749</v>
       </c>
       <c r="V26" t="n">
         <v>2.1696</v>
